--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2019_T1_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2019_T1_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>85</t>
+    <t>81</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.445</t>
-  </si>
-  <si>
-    <t>(3.258)</t>
-  </si>
-  <si>
-    <t>12.318</t>
-  </si>
-  <si>
-    <t>(1.607)</t>
-  </si>
-  <si>
-    <t>74.502</t>
-  </si>
-  <si>
-    <t>(25.417)</t>
-  </si>
-  <si>
-    <t>91.959</t>
-  </si>
-  <si>
-    <t>(31.587)</t>
-  </si>
-  <si>
-    <t>2.406</t>
-  </si>
-  <si>
-    <t>(0.292)</t>
-  </si>
-  <si>
-    <t>14.835</t>
-  </si>
-  <si>
-    <t>(1.763)</t>
-  </si>
-  <si>
-    <t>8.931</t>
-  </si>
-  <si>
-    <t>(3.522)</t>
-  </si>
-  <si>
-    <t>0.675</t>
-  </si>
-  <si>
-    <t>(0.168)</t>
-  </si>
-  <si>
-    <t>100.177</t>
-  </si>
-  <si>
-    <t>(34.308)</t>
-  </si>
-  <si>
-    <t>87.722</t>
-  </si>
-  <si>
-    <t>(30.334)</t>
+    <t>2.258</t>
+  </si>
+  <si>
+    <t>(0.330)</t>
+  </si>
+  <si>
+    <t>12.864</t>
+  </si>
+  <si>
+    <t>(1.662)</t>
+  </si>
+  <si>
+    <t>42.743</t>
+  </si>
+  <si>
+    <t>(8.349)</t>
+  </si>
+  <si>
+    <t>53.290</t>
+  </si>
+  <si>
+    <t>(9.854)</t>
+  </si>
+  <si>
+    <t>2.459</t>
+  </si>
+  <si>
+    <t>(0.300)</t>
+  </si>
+  <si>
+    <t>15.444</t>
+  </si>
+  <si>
+    <t>(1.820)</t>
+  </si>
+  <si>
+    <t>5.227</t>
+  </si>
+  <si>
+    <t>(1.487)</t>
+  </si>
+  <si>
+    <t>0.603</t>
+  </si>
+  <si>
+    <t>(0.146)</t>
+  </si>
+  <si>
+    <t>61.804</t>
+  </si>
+  <si>
+    <t>(11.139)</t>
+  </si>
+  <si>
+    <t>46.590</t>
+  </si>
+  <si>
+    <t>(9.252)</t>
   </si>
   <si>
     <t>29</t>
@@ -198,7 +198,7 @@
     <t>(17.687)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-2.910</t>
-  </si>
-  <si>
-    <t>1.648</t>
-  </si>
-  <si>
-    <t>15.035</t>
-  </si>
-  <si>
-    <t>6.094</t>
-  </si>
-  <si>
-    <t>-0.505</t>
-  </si>
-  <si>
-    <t>-1.422</t>
-  </si>
-  <si>
-    <t>-5.464</t>
-  </si>
-  <si>
-    <t>-0.062</t>
-  </si>
-  <si>
-    <t>16.579</t>
-  </si>
-  <si>
-    <t>-6.691</t>
+    <t>0.277</t>
+  </si>
+  <si>
+    <t>1.101</t>
+  </si>
+  <si>
+    <t>46.794**</t>
+  </si>
+  <si>
+    <t>44.763**</t>
+  </si>
+  <si>
+    <t>-0.558</t>
+  </si>
+  <si>
+    <t>-2.031</t>
+  </si>
+  <si>
+    <t>-1.760</t>
+  </si>
+  <si>
+    <t>0.010</t>
+  </si>
+  <si>
+    <t>54.951**</t>
+  </si>
+  <si>
+    <t>34.440*</t>
   </si>
 </sst>
 </file>
